--- a/Borrame_cambiod e etiquetas.xlsx
+++ b/Borrame_cambiod e etiquetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\JVP\ANTIGRAVITY\BackCQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5FB5C8A-021A-433A-A7AE-699CBA9A0541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DC07803-6AAE-4448-A307-B28D08A5167A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{38ED77CC-4FCC-4E1C-B547-DFD76465D758}"/>
   </bookViews>
